--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_business_consumer_services.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.264</v>
+        <v>-0.243</v>
       </c>
       <c r="G2">
-        <v>0.3156146179401993</v>
+        <v>-0.4488836662749706</v>
       </c>
       <c r="H2">
-        <v>0.3156146179401993</v>
+        <v>-0.4488836662749706</v>
       </c>
       <c r="I2">
-        <v>-0.3311184939091916</v>
+        <v>-0.5229142185663925</v>
       </c>
       <c r="J2">
-        <v>-0.3311184939091916</v>
+        <v>-0.5229142185663925</v>
       </c>
       <c r="K2">
-        <v>-3.71</v>
+        <v>-6.95</v>
       </c>
       <c r="L2">
-        <v>-0.4108527131782946</v>
+        <v>-0.8166862514688602</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.459</v>
+        <v>0.697</v>
       </c>
       <c r="V2">
-        <v>0.02798780487804878</v>
+        <v>0.1072307692307692</v>
       </c>
       <c r="W2">
-        <v>-0.2072625698324022</v>
+        <v>-0.54296875</v>
       </c>
       <c r="X2">
-        <v>0.1988820994393913</v>
+        <v>0.1930515450518905</v>
       </c>
       <c r="Y2">
-        <v>-0.4061446692717936</v>
+        <v>-0.7360202950518905</v>
       </c>
       <c r="Z2">
-        <v>0.2175222219545684</v>
+        <v>0.2522154055896387</v>
       </c>
       <c r="AA2">
-        <v>-0.0720256305253776</v>
+        <v>-0.1318870217243117</v>
       </c>
       <c r="AB2">
-        <v>0.1215771894465938</v>
+        <v>0.1033139623756713</v>
       </c>
       <c r="AC2">
-        <v>-0.1936028199719714</v>
+        <v>-0.235200984099983</v>
       </c>
       <c r="AD2">
-        <v>21.4</v>
+        <v>12.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21.4</v>
+        <v>12.7</v>
       </c>
       <c r="AG2">
-        <v>20.941</v>
+        <v>12.003</v>
       </c>
       <c r="AH2">
-        <v>0.5661375661375662</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="AI2">
-        <v>0.6239067055393586</v>
+        <v>0.7277936962750716</v>
       </c>
       <c r="AJ2">
-        <v>0.5608044776519109</v>
+        <v>0.6487056153056261</v>
       </c>
       <c r="AK2">
-        <v>0.6188055908513341</v>
+        <v>0.7164686921745359</v>
       </c>
       <c r="AL2">
-        <v>0.863</v>
+        <v>0.575</v>
       </c>
       <c r="AM2">
-        <v>0.862</v>
+        <v>0.574</v>
       </c>
       <c r="AN2">
-        <v>-31.1046511627907</v>
+        <v>-5</v>
       </c>
       <c r="AO2">
-        <v>-3.464658169177289</v>
+        <v>-7.739130434782609</v>
       </c>
       <c r="AP2">
-        <v>-30.4375</v>
+        <v>-4.725590551181102</v>
       </c>
       <c r="AQ2">
-        <v>-3.468677494199536</v>
+        <v>-7.752613240418119</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.264</v>
+        <v>-0.243</v>
       </c>
       <c r="G3">
-        <v>0.3156146179401993</v>
+        <v>-0.4488836662749706</v>
       </c>
       <c r="H3">
-        <v>0.3156146179401993</v>
+        <v>-0.4488836662749706</v>
       </c>
       <c r="I3">
-        <v>-0.3311184939091916</v>
+        <v>-0.5229142185663925</v>
       </c>
       <c r="J3">
-        <v>-0.3311184939091916</v>
+        <v>-0.5229142185663925</v>
       </c>
       <c r="K3">
-        <v>-3.71</v>
+        <v>-6.95</v>
       </c>
       <c r="L3">
-        <v>-0.4108527131782946</v>
+        <v>-0.8166862514688602</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.459</v>
+        <v>0.697</v>
       </c>
       <c r="V3">
-        <v>0.02798780487804878</v>
+        <v>0.1072307692307692</v>
       </c>
       <c r="W3">
-        <v>-0.2072625698324022</v>
+        <v>-0.54296875</v>
       </c>
       <c r="X3">
-        <v>0.1988820994393913</v>
+        <v>0.1930515450518905</v>
       </c>
       <c r="Y3">
-        <v>-0.4061446692717936</v>
+        <v>-0.7360202950518905</v>
       </c>
       <c r="Z3">
-        <v>0.2175222219545684</v>
+        <v>0.2522154055896387</v>
       </c>
       <c r="AA3">
-        <v>-0.0720256305253776</v>
+        <v>-0.1318870217243117</v>
       </c>
       <c r="AB3">
-        <v>0.1215771894465938</v>
+        <v>0.1033139623756713</v>
       </c>
       <c r="AC3">
-        <v>-0.1936028199719714</v>
+        <v>-0.235200984099983</v>
       </c>
       <c r="AD3">
-        <v>21.4</v>
+        <v>12.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.4</v>
+        <v>12.7</v>
       </c>
       <c r="AG3">
-        <v>20.941</v>
+        <v>12.003</v>
       </c>
       <c r="AH3">
-        <v>0.5661375661375662</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="AI3">
-        <v>0.6239067055393586</v>
+        <v>0.7277936962750716</v>
       </c>
       <c r="AJ3">
-        <v>0.5608044776519109</v>
+        <v>0.6487056153056261</v>
       </c>
       <c r="AK3">
-        <v>0.6188055908513341</v>
+        <v>0.7164686921745359</v>
       </c>
       <c r="AL3">
-        <v>0.863</v>
+        <v>0.575</v>
       </c>
       <c r="AM3">
-        <v>0.862</v>
+        <v>0.574</v>
       </c>
       <c r="AN3">
-        <v>-31.1046511627907</v>
+        <v>-5</v>
       </c>
       <c r="AO3">
-        <v>-3.464658169177289</v>
+        <v>-7.739130434782609</v>
       </c>
       <c r="AP3">
-        <v>-30.4375</v>
+        <v>-4.725590551181102</v>
       </c>
       <c r="AQ3">
-        <v>-3.468677494199536</v>
+        <v>-7.752613240418119</v>
       </c>
     </row>
   </sheetData>
